--- a/data/trans_dic/IP1018-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP1018-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen problemas de riñón</t>
+          <t>Menores que padecen problemas de riñón (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,33</t>
+          <t>0,0; 2,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,2</t>
+          <t>0,0; 1,18</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,42</t>
+          <t>0,0; 1,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,57</t>
+          <t>0,0; 1,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 1,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,85</t>
+          <t>0,0; 0,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,79</t>
+          <t>0,0; 0,74</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,72</t>
+          <t>0,0; 2,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,87</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,85</t>
+          <t>0,0; 1,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,84</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,89</t>
+          <t>0,0; 2,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,36</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,51</t>
+          <t>0,0; 1,94</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,06</t>
+          <t>0,0; 2,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,61</t>
+          <t>0,0; 1,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,07</t>
+          <t>0,0; 1,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,38</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,85</t>
+          <t>0,0; 0,86</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,72</t>
+          <t>0,0; 0,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,78</t>
+          <t>0,08; 0,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,8</t>
+          <t>0,07; 0,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,86</t>
+          <t>0,0; 0,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,53</t>
+          <t>0,09; 0,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,54</t>
+          <t>0,08; 0,55</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen problemas de riñón (tasa de respuesta: 99,76%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>604</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>604</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2873</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3030</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>583</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1399</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>583</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3505</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2915</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4338</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4926</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3456</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1088</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1726</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3323</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3231</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5436</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3424</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 7338</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1244</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1244</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4434</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2981</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4130</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2977</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1374</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1824</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1923</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1676</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>3296</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4734</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>582; 5424</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>523; 5458</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5501</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>1241; 7242</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1178; 7953</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1018-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP1018-Edad-trans_dic.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,18</t>
+          <t>0,0; 2,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,18</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,38</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,38</t>
+          <t>0,0; 1,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,71</t>
+          <t>0,0; 1,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,97</t>
+          <t>0,0; 1,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,74</t>
+          <t>0,0; 0,67</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,61</t>
+          <t>0,0; 3,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,71</t>
+          <t>0,0; 2,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -923,12 +923,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,88</t>
+          <t>0,0; 2,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,27</t>
+          <t>0,0; 1,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,94</t>
+          <t>0,0; 1,63</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,71</t>
+          <t>0,0; 2,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,03</t>
+          <t>0,0; 1,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,86</t>
+          <t>0,0; 0,85</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,7</t>
+          <t>0,0; 0,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1128,12 +1128,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,77</t>
+          <t>0,08; 0,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,76</t>
+          <t>0,07; 0,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,74</t>
+          <t>0,0; 0,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,52</t>
+          <t>0,09; 0,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,55</t>
+          <t>0,08; 0,57</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2873</t>
+          <t>0; 3114</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3030</t>
+          <t>0; 3052</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3505</t>
+          <t>0; 3857</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1590,12 +1590,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2915</t>
+          <t>0; 2728</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4338</t>
+          <t>0; 3383</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4926</t>
+          <t>0; 5537</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 3456</t>
+          <t>0; 3143</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3323</t>
+          <t>0; 3955</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3231</t>
+          <t>0; 3933</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5436</t>
+          <t>0; 4685</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3424</t>
+          <t>0; 3499</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 7338</t>
+          <t>0; 6171</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4434</t>
+          <t>0; 4430</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1931,12 +1931,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 2981</t>
+          <t>0; 3566</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4130</t>
+          <t>0; 4096</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 2977</t>
+          <t>0; 2951</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4734</t>
+          <t>0; 4837</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>582; 5424</t>
+          <t>583; 5521</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>523; 5458</t>
+          <t>523; 4896</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2094,12 +2094,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 5501</t>
+          <t>0; 5588</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1241; 7242</t>
+          <t>1200; 7576</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1178; 7953</t>
+          <t>1193; 8226</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1018-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP1018-Edad-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -635,22 +635,22 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>0,46%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 1,2</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>0,28%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>0,28%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,52</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,33</t>
+          <t>0,0; 1,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,09</t>
+          <t>0,0; 0,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,67</t>
+          <t>0,0; 0,79</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,51%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,1</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,08</t>
+          <t>0,0; 2,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -923,12 +923,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,48</t>
+          <t>0,0; 1,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,3</t>
+          <t>0,0; 1,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,63</t>
+          <t>0,0; 1,51</t>
         </is>
       </c>
     </row>
@@ -955,7 +955,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -965,12 +965,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1018,12 +1018,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1033,12 +1033,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,02</t>
+          <t>0,0; 1,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>0,26%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,71</t>
+          <t>0,07; 0,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1128,27 +1128,27 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>0,0; 0,86</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 0,72</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>0,08; 0,78</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0,07; 0,68</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,75</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,54</t>
+          <t>0,05; 0,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,57</t>
+          <t>0,08; 0,54</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1321,22 +1321,22 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1374,22 +1374,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
           <t>604</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3114</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3067</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3052</t>
+          <t>0; 3059</t>
         </is>
       </c>
     </row>
@@ -1484,22 +1484,22 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>720</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>583</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3857</t>
+          <t>0; 3026</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1590,12 +1590,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2728</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3383</t>
+          <t>0; 3606</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1605,12 +1605,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3297</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5537</t>
+          <t>0; 4300</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 3143</t>
+          <t>0; 3705</t>
         </is>
       </c>
     </row>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1088</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>654</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>638</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1088</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3955</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3933</t>
+          <t>0; 5441</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3473</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4685</t>
+          <t>0; 3502</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3499</t>
+          <t>0; 3663</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 6171</t>
+          <t>0; 5687</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1863,12 +1863,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>588</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4252</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2804</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4430</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1931,12 +1931,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3566</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4096</t>
+          <t>0; 4269</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 2951</t>
+          <t>0; 2961</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1923</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1676</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>1374</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>1824</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1923</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1676</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4837</t>
+          <t>525; 5757</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>583; 5521</t>
+          <t>0; 6377</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>523; 4896</t>
+          <t>0; 4869</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2094,12 +2094,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 5588</t>
+          <t>582; 5523</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1200; 7576</t>
+          <t>721; 7477</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1193; 8226</t>
+          <t>1224; 7871</t>
         </is>
       </c>
     </row>
